--- a/exports/SRF_full_report.xlsx
+++ b/exports/SRF_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>7.12</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>2522.2</v>
+        <v>2477.65</v>
       </c>
       <c r="I2" t="n">
         <v>2514.982809633492</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5</v>
+        <v>-2.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.86</v>
+        <v>2.63</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.75</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44600.38541666666</v>
+        <v>44600.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2487.65</v>
+        <v>2535</v>
       </c>
       <c r="I3" t="n">
         <v>2528.323341135868</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4</v>
+        <v>-2.31</v>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
         <v>1.48</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2473.6</v>
+        <v>2397</v>
       </c>
       <c r="I4" t="n">
         <v>2414.99294221524</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.42</v>
+        <v>-5.44</v>
       </c>
       <c r="L4" t="n">
-        <v>2.88</v>
+        <v>6.07</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77</v>
+        <v>2.57</v>
       </c>
       <c r="N4" t="n">
-        <v>4.12</v>
+        <v>5.39</v>
       </c>
       <c r="O4" t="n">
         <v>3.47</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2250</v>
+        <v>2334</v>
       </c>
       <c r="I5" t="n">
         <v>2332.441096681749</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>6.13</v>
+        <v>2.63</v>
       </c>
       <c r="L5" t="n">
         <v>5.13</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.07</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2613</v>
+        <v>2541.45</v>
       </c>
       <c r="I6" t="n">
         <v>2594.925089525324</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>11.95</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>3.94</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.25</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44698.55208333334</v>
+        <v>44699.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2326</v>
+        <v>2351.1</v>
       </c>
       <c r="I7" t="n">
         <v>2331.270278868293</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>8.48</v>
+        <v>7.49</v>
       </c>
       <c r="L7" t="n">
         <v>4.52</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44719.55208333334</v>
+        <v>44720.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2329</v>
+        <v>2299.7</v>
       </c>
       <c r="I8" t="n">
         <v>2299.963180928012</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.19</v>
       </c>
       <c r="L8" t="n">
         <v>6.89</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.24</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2280</v>
+        <v>2308.05</v>
       </c>
       <c r="I9" t="n">
         <v>2300.61856720087</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>0.86</v>
+        <v>-0.36</v>
       </c>
       <c r="L9" t="n">
         <v>2.19</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.98</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44743.38541666666</v>
+        <v>44743.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>2176.85</v>
+        <v>2161.4</v>
       </c>
       <c r="I10" t="n">
         <v>2170.906676037054</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.68</v>
+        <v>-6.35</v>
       </c>
       <c r="L10" t="n">
         <v>7.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.62</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44754.55208333334</v>
+        <v>44755.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2191</v>
+        <v>2224.9</v>
       </c>
       <c r="I11" t="n">
         <v>2191.058233146067</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.37</v>
+        <v>-2.94</v>
       </c>
       <c r="L11" t="n">
-        <v>2.68</v>
+        <v>3.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.3</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.08</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2447</v>
+        <v>2390.1</v>
       </c>
       <c r="I12" t="n">
         <v>2399.860388925169</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>9.98</v>
+        <v>7.43</v>
       </c>
       <c r="L12" t="n">
         <v>1.75</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>6.92</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2425</v>
+        <v>2551.75</v>
       </c>
       <c r="I13" t="n">
         <v>2520.058347931367</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.46</v>
+        <v>-6.76</v>
       </c>
       <c r="L13" t="n">
-        <v>2.67</v>
+        <v>6.9</v>
       </c>
       <c r="M13" t="n">
         <v>0.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>4.66</v>
       </c>
       <c r="O13" t="n">
         <v>-2.33</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44820.55208333334</v>
+        <v>44823.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2699.95</v>
+        <v>2663.2</v>
       </c>
       <c r="I14" t="n">
         <v>2678.351377255784</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>5.81</v>
+        <v>4.37</v>
       </c>
       <c r="L14" t="n">
         <v>4.57</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.95</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2591.65</v>
+        <v>2611.05</v>
       </c>
       <c r="I15" t="n">
         <v>2608.563260647587</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>2.69</v>
+        <v>1.96</v>
       </c>
       <c r="L15" t="n">
         <v>2.73</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>4.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44868.55208333334</v>
+        <v>44869.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2547</v>
+        <v>2484.4</v>
       </c>
       <c r="I16" t="n">
         <v>2487.184689689118</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.45</v>
+        <v>-4.85</v>
       </c>
       <c r="L16" t="n">
-        <v>3.76</v>
+        <v>6.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="N16" t="n">
         <v>2.54</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.8</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2354</v>
+        <v>2370</v>
       </c>
       <c r="I17" t="n">
         <v>2358.66208932936</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
         <v>2.27</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.49</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>2331.5</v>
+        <v>2320</v>
       </c>
       <c r="I18" t="n">
         <v>2326.549517792592</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.62</v>
+        <v>-2.11</v>
       </c>
       <c r="L18" t="n">
         <v>2.49</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.26</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44956.38541666666</v>
+        <v>44956.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2088</v>
+        <v>2184.5</v>
       </c>
       <c r="I19" t="n">
         <v>2180.101900801672</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>5.84</v>
       </c>
       <c r="L19" t="n">
         <v>1.25</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.5</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44980.55208333334</v>
+        <v>44981.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2250</v>
+        <v>2224.7</v>
       </c>
       <c r="I20" t="n">
         <v>2231.619457713889</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1.84</v>
       </c>
       <c r="L20" t="n">
         <v>4.69</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.55</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2250</v>
+        <v>2273.8</v>
       </c>
       <c r="I21" t="n">
         <v>2270.223855371775</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.14</v>
+        <v>-2.21</v>
       </c>
       <c r="L21" t="n">
-        <v>1.59</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
         <v>0.79</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.83</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2542.4</v>
+        <v>2466.2</v>
       </c>
       <c r="I22" t="n">
         <v>2501.230514564645</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K22" t="n">
-        <v>11.81</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>1.16</v>
@@ -1695,7 +1958,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>1.66</v>
+        <v>2.89</v>
       </c>
       <c r="O22" t="n">
         <v>1.02</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.08</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2515</v>
+        <v>2525.25</v>
       </c>
       <c r="I23" t="n">
         <v>2524.898594409303</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.98</v>
+        <v>-2.39</v>
       </c>
       <c r="L23" t="n">
         <v>3.36</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.97</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>2512.5</v>
+        <v>2470</v>
       </c>
       <c r="I24" t="n">
         <v>2482.92499580364</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5</v>
+        <v>-2.19</v>
       </c>
       <c r="L24" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="M24" t="n">
         <v>0.36</v>
       </c>
       <c r="N24" t="n">
-        <v>1.86</v>
+        <v>3.68</v>
       </c>
       <c r="O24" t="n">
         <v>0.6</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>2250</v>
+        <v>2264.2</v>
       </c>
       <c r="I25" t="n">
         <v>2251.376488822219</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>8.91</v>
+        <v>8.33</v>
       </c>
       <c r="L25" t="n">
         <v>2.27</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.09</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2436</v>
+        <v>2387</v>
       </c>
       <c r="I26" t="n">
         <v>2388.587562772116</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>7.59</v>
+        <v>5.42</v>
       </c>
       <c r="L26" t="n">
         <v>1.38</v>
@@ -1923,7 +2234,7 @@
         <v>0.43</v>
       </c>
       <c r="N26" t="n">
-        <v>0.92</v>
+        <v>2.63</v>
       </c>
       <c r="O26" t="n">
         <v>0.67</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.77</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45215.55208333334</v>
+        <v>45216.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>2247.7</v>
+        <v>2285.65</v>
       </c>
       <c r="I27" t="n">
         <v>2282.847612100904</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>5.84</v>
+        <v>4.25</v>
       </c>
       <c r="L27" t="n">
         <v>2.64</v>
@@ -1980,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="O27" t="n">
         <v>-2.63</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>3.88</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>2231.95</v>
+        <v>2187.55</v>
       </c>
       <c r="I28" t="n">
         <v>2203.724193557905</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.35</v>
+        <v>-4.29</v>
       </c>
       <c r="L28" t="n">
-        <v>2.97</v>
+        <v>4.39</v>
       </c>
       <c r="M28" t="n">
-        <v>0.26</v>
+        <v>0.53</v>
       </c>
       <c r="N28" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>2180</v>
+        <v>2240</v>
       </c>
       <c r="I29" t="n">
         <v>2206.85423397084</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
-        <v>0.35</v>
+        <v>-2.4</v>
       </c>
       <c r="L29" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="M29" t="n">
         <v>0.72</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.15</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45272.38541666666</v>
+        <v>45272.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>2414.75</v>
+        <v>2383</v>
       </c>
       <c r="I30" t="n">
         <v>2386.92869771233</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>7.8</v>
+        <v>6.38</v>
       </c>
       <c r="L30" t="n">
         <v>2.23</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>4.63</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>2490</v>
+        <v>2506.8</v>
       </c>
       <c r="I31" t="n">
         <v>2493.219447762356</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.49</v>
+        <v>-5.2</v>
       </c>
       <c r="L31" t="n">
         <v>6.13</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45299.38541666666</v>
+        <v>45299.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>2422</v>
+        <v>2393.5</v>
       </c>
       <c r="I32" t="n">
         <v>2406.493240965305</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.38</v>
+        <v>-4.52</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>4.86</v>
       </c>
       <c r="M32" t="n">
         <v>0.52</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.7</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45335.38541666666</v>
+        <v>45335.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>2310.6</v>
+        <v>2325</v>
       </c>
       <c r="I33" t="n">
         <v>2323.457091878302</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>3.46</v>
+        <v>2.86</v>
       </c>
       <c r="L33" t="n">
         <v>1.69</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.76</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2586</v>
+        <v>2407.6</v>
       </c>
       <c r="I34" t="n">
         <v>2554.569799836041</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>83</v>
+        <v>83.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>11.23</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.17</v>
@@ -2379,7 +2786,7 @@
         <v>1.86</v>
       </c>
       <c r="N34" t="n">
-        <v>3.67</v>
+        <v>7.19</v>
       </c>
       <c r="O34" t="n">
         <v>1.85</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45450.38541666666</v>
+        <v>45450.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>2290.5</v>
+        <v>2310</v>
       </c>
       <c r="I35" t="n">
         <v>2301.171040092102</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>4.86</v>
+        <v>4.05</v>
       </c>
       <c r="L35" t="n">
         <v>5.5</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45481.38541666666</v>
+        <v>45481.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>2401</v>
+        <v>2369</v>
       </c>
       <c r="I36" t="n">
         <v>2375.649034649158</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>30.83333333333333</v>
+        <v>31</v>
       </c>
       <c r="K36" t="n">
-        <v>3.94</v>
+        <v>2.55</v>
       </c>
       <c r="L36" t="n">
         <v>0.87</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>5.15</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>2400</v>
+        <v>2464.4</v>
       </c>
       <c r="I37" t="n">
         <v>2439.933915537453</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.31</v>
+        <v>-4.03</v>
       </c>
       <c r="L37" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="M37" t="n">
         <v>0.78</v>
       </c>
       <c r="N37" t="n">
-        <v>1.44</v>
+        <v>2.46</v>
       </c>
       <c r="O37" t="n">
         <v>-1.09</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>6.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2526.9</v>
+        <v>2443.9</v>
       </c>
       <c r="I38" t="n">
         <v>2491.14516599794</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K38" t="n">
-        <v>2.54</v>
+        <v>-0.83</v>
       </c>
       <c r="L38" t="n">
         <v>2.61</v>
       </c>
       <c r="M38" t="n">
-        <v>1.16</v>
+        <v>2.64</v>
       </c>
       <c r="N38" t="n">
         <v>3.39</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.35</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45537.55208333334</v>
+        <v>45538.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2585.4</v>
+        <v>2601.9</v>
       </c>
       <c r="I39" t="n">
         <v>2586.205037910158</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.79</v>
+        <v>-6.47</v>
       </c>
       <c r="L39" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="M39" t="n">
         <v>1.37</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>4.91</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>2505.55</v>
+        <v>2502.5</v>
       </c>
       <c r="I40" t="n">
         <v>2504.111749917802</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.7</v>
+        <v>-3.82</v>
       </c>
       <c r="L40" t="n">
-        <v>3.87</v>
+        <v>5.27</v>
       </c>
       <c r="M40" t="n">
         <v>0.83</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>2485</v>
+        <v>2496.3</v>
       </c>
       <c r="I41" t="n">
         <v>2493.249610209809</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="L41" t="n">
         <v>2.5</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.34</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2421.75</v>
+        <v>2377.25</v>
       </c>
       <c r="I42" t="n">
         <v>2395.504843773918</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.99</v>
+        <v>-4.77</v>
       </c>
       <c r="L42" t="n">
-        <v>3.36</v>
+        <v>4.85</v>
       </c>
       <c r="M42" t="n">
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.15</v>
+        <v>2.96</v>
       </c>
       <c r="O42" t="n">
         <v>0.4</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>6.14</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45601.55208333334</v>
+        <v>45602.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2305.2</v>
+        <v>2339.55</v>
       </c>
       <c r="I43" t="n">
         <v>2335.883784329217</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K43" t="n">
-        <v>3.03</v>
+        <v>1.59</v>
       </c>
       <c r="L43" t="n">
         <v>2.39</v>
       </c>
       <c r="M43" t="n">
-        <v>0.71</v>
+        <v>1.27</v>
       </c>
       <c r="N43" t="n">
         <v>2.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.86</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45608.38541666666</v>
+        <v>45608.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>2265.2</v>
+        <v>2241</v>
       </c>
       <c r="I44" t="n">
         <v>2258.111782518597</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.18</v>
+        <v>-4.21</v>
       </c>
       <c r="L44" t="n">
-        <v>3.48</v>
+        <v>4.32</v>
       </c>
       <c r="M44" t="n">
         <v>-0</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.1</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>2236</v>
+        <v>2282.6</v>
       </c>
       <c r="I45" t="n">
         <v>2270.023677856541</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.22</v>
+        <v>-1.86</v>
       </c>
       <c r="L45" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="M45" t="n">
         <v>0.93</v>
       </c>
       <c r="N45" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="O45" t="n">
         <v>-2.31</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45650.55208333334</v>
+        <v>45652.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2272.95</v>
+        <v>2251.35</v>
       </c>
       <c r="I46" t="n">
         <v>2258.680771506072</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.42</v>
+        <v>-1.37</v>
       </c>
       <c r="L46" t="n">
         <v>3.53</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2304</v>
+        <v>2341.05</v>
       </c>
       <c r="I47" t="n">
         <v>2321.17366027616</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.34</v>
+        <v>-3.98</v>
       </c>
       <c r="L47" t="n">
         <v>4.82</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2839.8</v>
+        <v>2730.9</v>
       </c>
       <c r="I48" t="n">
         <v>2771.491871430904</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K48" t="n">
-        <v>21.3</v>
+        <v>16.65</v>
       </c>
       <c r="L48" t="n">
         <v>1.83</v>
@@ -3177,7 +3752,7 @@
         <v>5.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>3.16</v>
       </c>
       <c r="O48" t="n">
         <v>2.26</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2854.95</v>
+        <v>2922.65</v>
       </c>
       <c r="I49" t="n">
         <v>2875.58343689422</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.54</v>
+        <v>-7.02</v>
       </c>
       <c r="L49" t="n">
-        <v>6.25</v>
+        <v>7.44</v>
       </c>
       <c r="M49" t="n">
         <v>1.24</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.63</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>2886.75</v>
+        <v>2880</v>
       </c>
       <c r="I50" t="n">
         <v>2883.905216846338</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="L50" t="n">
         <v>3.91</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.49</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2730.95</v>
+        <v>2928.3</v>
       </c>
       <c r="I51" t="n">
         <v>2927.30213986423</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>5.18</v>
+        <v>-1.68</v>
       </c>
       <c r="L51" t="n">
         <v>2.78</v>
       </c>
       <c r="M51" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
-        <v>1.29</v>
+        <v>7.8</v>
       </c>
       <c r="O51" t="n">
         <v>-1.84</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.65</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45790.55208333334</v>
+        <v>45791.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>2924.9</v>
+        <v>2878.2</v>
       </c>
       <c r="I52" t="n">
         <v>2882.57631918409</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.12</v>
+        <v>-1.71</v>
       </c>
       <c r="L52" t="n">
         <v>4.16</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.09</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45811.55208333334</v>
+        <v>45812.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2951</v>
+        <v>3026</v>
       </c>
       <c r="I53" t="n">
         <v>2973.346697422593</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.53</v>
+        <v>-5.14</v>
       </c>
       <c r="L53" t="n">
         <v>5.34</v>
@@ -3462,7 +4097,7 @@
         <v>0.9</v>
       </c>
       <c r="N53" t="n">
-        <v>2.26</v>
+        <v>3.47</v>
       </c>
       <c r="O53" t="n">
         <v>-1.47</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.69</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>3198.8</v>
+        <v>3167.5</v>
       </c>
       <c r="I54" t="n">
         <v>3170.191464030831</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>5.71</v>
+        <v>4.68</v>
       </c>
       <c r="L54" t="n">
         <v>2.14</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.84</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2926</v>
+        <v>2966.6</v>
       </c>
       <c r="I55" t="n">
         <v>2964.338173812571</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>60</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>7.62</v>
+        <v>6.34</v>
       </c>
       <c r="L55" t="n">
         <v>2.93</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.21</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>2873</v>
+        <v>2834</v>
       </c>
       <c r="I56" t="n">
         <v>2872.608752704267</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.16</v>
+        <v>-4.47</v>
       </c>
       <c r="L56" t="n">
-        <v>3.39</v>
+        <v>4.59</v>
       </c>
       <c r="M56" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>1.34</v>
+        <v>2.21</v>
       </c>
       <c r="O56" t="n">
         <v>1.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>4.7</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2916.7</v>
+        <v>2932.8</v>
       </c>
       <c r="I57" t="n">
         <v>2917.864856417357</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.92</v>
+        <v>-3.49</v>
       </c>
       <c r="L57" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="M57" t="n">
         <v>0.21</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.35</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45953.38541666666</v>
+        <v>45953.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>3097.9</v>
+        <v>3068.6</v>
       </c>
       <c r="I58" t="n">
         <v>3073.034128119861</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>5.63</v>
+        <v>4.63</v>
       </c>
       <c r="L58" t="n">
         <v>0.84</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.31</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2834.9</v>
+        <v>2918.4</v>
       </c>
       <c r="I59" t="n">
         <v>2897.606578128974</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K59" t="n">
-        <v>7.62</v>
+        <v>4.89</v>
       </c>
       <c r="L59" t="n">
         <v>1.35</v>
       </c>
       <c r="M59" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="N59" t="n">
-        <v>2.23</v>
+        <v>3.46</v>
       </c>
       <c r="O59" t="n">
         <v>-2.4</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.43</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3068.7</v>
+        <v>3005</v>
       </c>
       <c r="I60" t="n">
         <v>3011.378957226935</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>5.15</v>
+        <v>2.97</v>
       </c>
       <c r="L60" t="n">
         <v>3.88</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,25 +4628,25 @@
         <v>5.63</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>2799.2</v>
+        <v>2923.6</v>
       </c>
       <c r="I61" t="n">
         <v>2836.767904504725</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>6.85</v>
+        <v>2.71</v>
       </c>
       <c r="L61" t="n">
         <v>3.69</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8100000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="N61" t="n">
         <v>5.59</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.01</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46070.38541666666</v>
+        <v>46070.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>2876</v>
+        <v>2735.8</v>
       </c>
       <c r="I62" t="n">
         <v>2811.592788091949</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.63</v>
+        <v>-6.42</v>
       </c>
       <c r="L62" t="n">
-        <v>5.4</v>
+        <v>6.58</v>
       </c>
       <c r="M62" t="n">
         <v>0.97</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>2479.8</v>
+        <v>2568.5</v>
       </c>
       <c r="I63" t="n">
         <v>2561.866419350279</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>9.359999999999999</v>
+        <v>6.12</v>
       </c>
       <c r="L63" t="n">
         <v>5.38</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>2415</v>
+        <v>2383.1</v>
       </c>
       <c r="I64" t="n">
         <v>2402.586017264282</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.98</v>
+        <v>-7.22</v>
       </c>
       <c r="L64" t="n">
-        <v>6.74</v>
+        <v>8.31</v>
       </c>
       <c r="M64" t="n">
         <v>2.94</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.93</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46147.55208333334</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>2536.2</v>
+        <v>2737.8</v>
       </c>
       <c r="I65" t="n">
         <v>2579.244642786538</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.42</v>
+        <v>-14.88</v>
       </c>
       <c r="L65" t="n">
-        <v>9.27</v>
+        <v>15.9</v>
       </c>
       <c r="M65" t="n">
         <v>4.17</v>
       </c>
       <c r="N65" t="n">
-        <v>2.83</v>
+        <v>7.44</v>
       </c>
       <c r="O65" t="n">
         <v>0.82</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>2632</v>
+        <v>2610.8</v>
       </c>
       <c r="I66" t="n">
         <v>2626.725259547982</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.86</v>
+        <v>-4.64</v>
       </c>
       <c r="L66" t="n">
         <v>5.68</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.23</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46168.38541666666</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>2740</v>
+        <v>2749.4</v>
       </c>
       <c r="I67" t="n">
         <v>2742.567357544483</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.95</v>
+        <v>-5.31</v>
       </c>
       <c r="L67" t="n">
         <v>6.21</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>4.45</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>2818</v>
+        <v>2667</v>
       </c>
       <c r="I68" t="n">
         <v>2795.237080019005</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K68" t="n">
-        <v>2.5</v>
+        <v>-3</v>
       </c>
       <c r="L68" t="n">
         <v>5.06</v>
@@ -4317,7 +5132,7 @@
         <v>2.04</v>
       </c>
       <c r="N68" t="n">
-        <v>4.38</v>
+        <v>6.94</v>
       </c>
       <c r="O68" t="n">
         <v>1.12</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>12.12</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46283.38541666666</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>2549.8</v>
+        <v>2558.7</v>
       </c>
       <c r="I69" t="n">
         <v>2556.242700777119</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K69" t="n">
-        <v>4.39</v>
+        <v>4.06</v>
       </c>
       <c r="L69" t="n">
         <v>7.44</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>3.87</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>2502</v>
+        <v>2452</v>
       </c>
       <c r="I70" t="n">
         <v>2470.221326995131</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.22</v>
+        <v>-4.17</v>
       </c>
       <c r="L70" t="n">
-        <v>2.79</v>
+        <v>5.5</v>
       </c>
       <c r="M70" t="n">
         <v>1.09</v>
       </c>
       <c r="N70" t="n">
-        <v>1.13</v>
+        <v>2.46</v>
       </c>
       <c r="O70" t="n">
         <v>1.13</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>38</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.85</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.93</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.77</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.3</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.54</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.97</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.27</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.11</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.04</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
